--- a/docs/Canevas_Extraction_mSupply_DQA_v2.xlsx
+++ b/docs/Canevas_Extraction_mSupply_DQA_v2.xlsx
@@ -147,7 +147,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">CANEVAS D'EXTRACTION mSupply — TABLEAU DE BORD DQA</t>
+          <t xml:space="preserve">CANEVAS D'EXTRACTION mSupply · TABLEAU DE BORD DQA</t>
         </is>
       </c>
       <c r="B1" s="0"/>
@@ -155,7 +155,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nouvelle PSP-CI / DAP — Spécification v2.0 (2026-08-28)</t>
+          <t xml:space="preserve">Nouvelle PSP-CI / DAP · Spécification v2.0 (2026-08-28)</t>
         </is>
       </c>
       <c r="B2" s="0"/>
@@ -256,7 +256,7 @@
       <c r="A17" s="0"/>
       <c r="B17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">4 mois consécutifs, notés M+1 à M+4. Trois cycles par an sur l'année civile : C1 janvier–avril, C2 mai–août, C3 septembre–décembre.</t>
+          <t xml:space="preserve">4 mois consécutifs, notés M+1 à M+4. Trois cycles par an sur l'année civile : C1 janvier-avril, C2 mai-août, C3 septembre-décembre.</t>
         </is>
       </c>
     </row>
@@ -422,7 +422,7 @@
       </c>
       <c r="B33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Détail produit des transactions — PRODUITS TRACEURS UNIQUEMENT.</t>
+          <t xml:space="preserve">Détail produit des transactions (PRODUITS TRACEURS UNIQUEMENT).</t>
         </is>
       </c>
     </row>
@@ -434,7 +434,7 @@
       </c>
       <c r="B34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stock disponible à la date d'extraction — TRACEURS UNIQUEMENT.</t>
+          <t xml:space="preserve">Stock disponible à la date d'extraction (TRACEURS UNIQUEMENT).</t>
         </is>
       </c>
     </row>
@@ -458,7 +458,7 @@
       </c>
       <c r="B36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Détail produit des inventaires — TRACEURS UNIQUEMENT, sans doublon.</t>
+          <t xml:space="preserve">Détail produit des inventaires (TRACEURS UNIQUEMENT, sans doublon).</t>
         </is>
       </c>
     </row>
@@ -597,7 +597,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">INVENTAIRE_LIGNES — une ligne (inventaire, produit, lot). TRACEURS UNIQUEMENT. Une seule ligne par clé, sans doublon.</t>
+          <t xml:space="preserve">INVENTAIRE_LIGNES · une ligne (inventaire, produit, lot). TRACEURS UNIQUEMENT. Une seule ligne par clé, sans doublon.</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">REQUISITIONS — une réquisition. Fenêtre = date_entered ou période couverte touchant la fenêtre.</t>
+          <t xml:space="preserve">REQUISITIONS · une réquisition. Fenêtre = date_entered ou période couverte touchant la fenêtre.</t>
         </is>
       </c>
     </row>
@@ -1240,7 +1240,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SITES — un site (magasin mSupply). Inclure tous les magasins actifs.</t>
+          <t xml:space="preserve">SITES · un site (magasin mSupply). Inclure tous les magasins actifs.</t>
         </is>
       </c>
     </row>
@@ -1250,7 +1250,7 @@
     <row r="4" ht="135" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Obligatoire. store.id — identifiant mSupply du magasin.</t>
+          <t xml:space="preserve">Obligatoire. store.id (identifiant mSupply du magasin).</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -1414,7 +1414,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SITE_PROGRAMME — un couple (site, programme géré). Pilote le pilier P1.</t>
+          <t xml:space="preserve">SITE_PROGRAMME · un couple (site, programme géré). Pilote le pilier P1.</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PRODUITS — un produit. Tous les produits (le marquage traceur est géré côté tableau de bord).</t>
+          <t xml:space="preserve">PRODUITS · un produit. Tous les produits (le marquage traceur est géré côté tableau de bord).</t>
         </is>
       </c>
     </row>
@@ -1651,7 +1651,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">TRANSACTIONS — une transaction (en-tête). Fenêtre = confirm_date ou finalised_date dans la fenêtre.</t>
+          <t xml:space="preserve">TRANSACTIONS · une transaction (en-tête). Fenêtre = confirm_date ou finalised_date dans la fenêtre.</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Obligatoire. Valeur dérivée — voir §5.1 de la spécification. Valeurs : dispensation, distribution, facture_fournisseur, reception, ajustement_positif, ajustement_negatif, retour_fournisseur, retour_client, autre.</t>
+          <t xml:space="preserve">Obligatoire. Valeur dérivée (voir §5.1 de la spécification). Valeurs : dispensation, distribution, facture_fournisseur, reception, ajustement_positif, ajustement_negatif, retour_fournisseur, retour_client, autre.</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -1901,7 +1901,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">LIGNES_TRANSACTIONS — une ligne (transaction, produit, lot). PRODUITS TRACEURS UNIQUEMENT.</t>
+          <t xml:space="preserve">LIGNES_TRANSACTIONS · une ligne (transaction, produit, lot). PRODUITS TRACEURS UNIQUEMENT.</t>
         </is>
       </c>
     </row>
@@ -1936,12 +1936,12 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Obligatoire. trans_line.quantity — quantité réelle en conditionnement.</t>
+          <t xml:space="preserve">Obligatoire. trans_line.quantity (quantité réelle en conditionnement).</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Obligatoire. trans_line.pack_size — unités de dispensation par conditionnement.</t>
+          <t xml:space="preserve">Obligatoire. trans_line.pack_size (unités de dispensation par conditionnement).</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -2091,7 +2091,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">STOCK_ACTUEL — un lot en stock (site, produit, lot) à la date d'extraction. TRACEURS UNIQUEMENT.</t>
+          <t xml:space="preserve">STOCK_ACTUEL · un lot en stock (site, produit, lot) à la date d'extraction. TRACEURS UNIQUEMENT.</t>
         </is>
       </c>
     </row>
@@ -2222,7 +2222,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">INVENTAIRES — un inventaire (stock_take, en-tête). Fenêtre = stock_take_date dans la fenêtre.</t>
+          <t xml:space="preserve">INVENTAIRES · un inventaire (stock_take, en-tête). Fenêtre = stock_take_date dans la fenêtre.</t>
         </is>
       </c>
     </row>

--- a/docs/Canevas_Extraction_mSupply_DQA_v2.xlsx
+++ b/docs/Canevas_Extraction_mSupply_DQA_v2.xlsx
@@ -1,66 +1,69 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <sheets>
-    <sheet name="MODE_EMPLOI" sheetId="1" r:id="rId1"/>
-    <sheet name="METADATA" sheetId="2" r:id="rId2"/>
-    <sheet name="SITES" sheetId="3" r:id="rId3"/>
-    <sheet name="SITE_PROGRAMME" sheetId="4" r:id="rId4"/>
-    <sheet name="PRODUITS" sheetId="5" r:id="rId5"/>
-    <sheet name="TRANSACTIONS" sheetId="6" r:id="rId6"/>
-    <sheet name="LIGNES_TRANSACTIONS" sheetId="7" r:id="rId7"/>
-    <sheet name="STOCK_ACTUEL" sheetId="8" r:id="rId8"/>
-    <sheet name="INVENTAIRES" sheetId="9" r:id="rId9"/>
-    <sheet name="INVENTAIRE_LIGNES" sheetId="10" r:id="rId10"/>
-    <sheet name="REQUISITIONS" sheetId="11" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MODE_EMPLOI" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="METADATA" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SITES" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SITE_PROGRAMME" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PRODUITS" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TRANSACTIONS" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LIGNES_TRANSACTIONS" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="STOCK_ACTUEL" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INVENTAIRES" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INVENTAIRE_LIGNES" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REQUISITIONS" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
+  <definedNames/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="7">
     <font>
+      <name val="Calibri"/>
       <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
-      <b/>
+      <name val="Calibri"/>
+      <b val="1"/>
       <sz val="14"/>
-      <name val="Calibri"/>
     </font>
     <font>
-      <i/>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="FF666666"/>
       <sz val="11"/>
-      <color rgb="FF666666"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <color rgb="FF555555"/>
       <sz val="9"/>
-      <color rgb="FF555555"/>
-      <name val="Calibri"/>
     </font>
     <font>
-      <b/>
+      <name val="Calibri"/>
+      <b val="1"/>
       <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
-      <i/>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="FF888888"/>
       <sz val="10"/>
-      <color rgb="FF888888"/>
-      <name val="Calibri"/>
     </font>
     <font>
-      <b/>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FF1F3864"/>
       <sz val="12"/>
-      <color rgb="FF1F3864"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="5">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -112,462 +115,774 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="9">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1" vertical="top"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1" vertical="top"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
+</file>
+
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="1F497D"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="EEECE1"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4F81BD"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="C0504D"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="9BBB59"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8064A2"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4BACC6"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="F79646"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000FF"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="800080"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+</a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B51"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="24" customWidth="1"/>
-    <col min="2" max="2" width="118" customWidth="1"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="118" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">CANEVAS D'EXTRACTION mSupply · TABLEAU DE BORD DQA</t>
-        </is>
-      </c>
-      <c r="B1" s="0"/>
+          <t>CANEVAS D'EXTRACTION mSupply · TABLEAU DE BORD DQA</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nouvelle PSP-CI / DAP · Spécification v2.0 (2026-08-28)</t>
-        </is>
-      </c>
-      <c r="B2" s="0"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="0"/>
-    </row>
+          <t>Nouvelle PSP-CI / DAP · Spécification v2.0 (2026-08-28)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">PRINCIPE</t>
-        </is>
-      </c>
-      <c r="B4" s="0"/>
+          <t>PRINCIPE</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="0"/>
-      <c r="B5" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ce classeur est le format attendu pour l'alimentation hebdomadaire du tableau de bord DQA (40 sites, six piliers PAQD).</t>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Ce classeur est le format attendu pour l'alimentation hebdomadaire du tableau de bord DQA (40 sites, six piliers PAQD).</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="0"/>
-      <c r="B6" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Chaque onglet correspond à une extraction mSupply. Les noms de colonnes (ligne 5 de chaque onglet) ne doivent être ni renommés, ni déplacés, ni supprimés.</t>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Chaque onglet correspond à une extraction mSupply. Les noms de colonnes (ligne 5 de chaque onglet) ne doivent être ni renommés, ni déplacés, ni supprimés.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="0"/>
-      <c r="B7" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Renseigner d'abord l'onglet METADATA. Coller le résultat de chaque requête à partir de la ligne 6, après avoir supprimé la ligne d'exemple.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="0"/>
-    </row>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Renseigner d'abord l'onglet METADATA. Coller le résultat de chaque requête à partir de la ligne 6, après avoir supprimé la ligne d'exemple.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">PÉRIODICITÉ</t>
-        </is>
-      </c>
-      <c r="B9" s="0"/>
+          <t>PÉRIODICITÉ</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="0"/>
-      <c r="B10" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Hebdomadaire, de préférence le même jour chaque semaine.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="0"/>
-    </row>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Hebdomadaire, de préférence le même jour chaque semaine.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">FENÊTRE D'EXTRACTION</t>
-        </is>
-      </c>
-      <c r="B12" s="0"/>
+          <t>FENÊTRE D'EXTRACTION</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="0"/>
-      <c r="B13" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Les 45 derniers jours à chaque extraction (et non « depuis le dernier envoi »). Ce recouvrement permet de rattraper une semaine oubliée.</t>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Les 45 derniers jours à chaque extraction (et non « depuis le dernier envoi »). Ce recouvrement permet de rattraper une semaine oubliée.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="0"/>
-      <c r="B14" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Les indicateurs sont calculés sur le MOIS PAQD déclaré dans METADATA, pas sur toute la fenêtre.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="0"/>
-    </row>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Les indicateurs sont calculés sur le MOIS PAQD déclaré dans METADATA, pas sur toute la fenêtre.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">CYCLE PAQD</t>
-        </is>
-      </c>
-      <c r="B16" s="0"/>
+          <t>CYCLE PAQD</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="0"/>
-      <c r="B17" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4 mois consécutifs, notés M+1 à M+4. Trois cycles par an sur l'année civile : C1 janvier-avril, C2 mai-août, C3 septembre-décembre.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="0"/>
-    </row>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>4 mois consécutifs, notés M+1 à M+4. Trois cycles par an sur l'année civile : C1 janvier-avril, C2 mai-août, C3 septembre-décembre.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">FORMAT DES DONNÉES</t>
-        </is>
-      </c>
-      <c r="B19" s="0"/>
+          <t>FORMAT DES DONNÉES</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dates</t>
-        </is>
-      </c>
-      <c r="B20" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Format AAAA-MM-JJ uniquement (ex. 2026-08-15). Jamais d'heure.</t>
+          <t>Dates</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Format AAAA-MM-JJ uniquement (ex. 2026-08-15). Jamais d'heure.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nombres</t>
-        </is>
-      </c>
-      <c r="B21" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Point décimal, sans séparateur de milliers, sans unité.</t>
+          <t>Nombres</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Point décimal, sans séparateur de milliers, sans unité.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valeur absente</t>
-        </is>
-      </c>
-      <c r="B22" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Laisser la cellule vide. Ne pas écrire « NULL », « N/A », « - » ou « néant ».</t>
+          <t>Valeur absente</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Laisser la cellule vide. Ne pas écrire « NULL », « N/A », « - » ou « néant ».</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Identifiants</t>
-        </is>
-      </c>
-      <c r="B23" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Reprendre exactement les identifiants mSupply (champ .id), sans reformatage.</t>
+          <t>Identifiants</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Reprendre exactement les identifiants mSupply (champ .id), sans reformatage.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Booléens</t>
-        </is>
-      </c>
-      <c r="B24" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OUI ou NON.</t>
+          <t>Booléens</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>OUI ou NON.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ligne d'exemple</t>
-        </is>
-      </c>
-      <c r="B25" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">La ligne 6 de chaque onglet (gris italique) est un exemple. La supprimer avant l'envoi.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="0"/>
-    </row>
+          <t>Ligne d'exemple</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>La ligne 6 de chaque onglet (gris italique) est un exemple. La supprimer avant l'envoi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ONGLETS À REMPLIR</t>
-        </is>
-      </c>
-      <c r="B27" s="0"/>
+          <t>ONGLETS À REMPLIR</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. METADATA</t>
-        </is>
-      </c>
-      <c r="B28" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Informations sur l'extraction et compteurs de lignes.</t>
+          <t>1. METADATA</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Informations sur l'extraction et compteurs de lignes.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2. SITES</t>
-        </is>
-      </c>
-      <c r="B29" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Référentiel des structures ; marque le périmètre DQA.</t>
+          <t>2. SITES</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Référentiel des structures ; marque le périmètre DQA.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">3. SITE_PROGRAMME</t>
-        </is>
-      </c>
-      <c r="B30" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Programmes de santé gérés par chaque site (pilote le pilier P1).</t>
+          <t>3. SITE_PROGRAMME</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Programmes de santé gérés par chaque site (pilote le pilier P1).</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">4. PRODUITS</t>
-        </is>
-      </c>
-      <c r="B31" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Référentiel des produits (tous).</t>
+          <t>4. PRODUITS</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Référentiel des produits (tous).</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">5. TRANSACTIONS</t>
-        </is>
-      </c>
-      <c r="B32" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Transactions de la fenêtre (en-têtes), qualifiées par « nature ».</t>
+          <t>5. TRANSACTIONS</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Transactions de la fenêtre (en-têtes), qualifiées par « nature ».</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">6. LIGNES_TRANSACTIONS</t>
-        </is>
-      </c>
-      <c r="B33" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Détail produit des transactions (PRODUITS TRACEURS UNIQUEMENT).</t>
+          <t>6. LIGNES_TRANSACTIONS</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Détail produit des transactions (PRODUITS TRACEURS UNIQUEMENT).</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">7. STOCK_ACTUEL</t>
-        </is>
-      </c>
-      <c r="B34" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Stock disponible à la date d'extraction (TRACEURS UNIQUEMENT).</t>
+          <t>7. STOCK_ACTUEL</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Stock disponible à la date d'extraction (TRACEURS UNIQUEMENT).</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">8. INVENTAIRES</t>
-        </is>
-      </c>
-      <c r="B35" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Inventaires de la fenêtre (en-têtes).</t>
+          <t>8. INVENTAIRES</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Inventaires de la fenêtre (en-têtes).</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">9. INVENTAIRE_LIGNES</t>
-        </is>
-      </c>
-      <c r="B36" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Détail produit des inventaires (TRACEURS UNIQUEMENT, sans doublon).</t>
+          <t>9. INVENTAIRE_LIGNES</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Détail produit des inventaires (TRACEURS UNIQUEMENT, sans doublon).</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">10. REQUISITIONS</t>
-        </is>
-      </c>
-      <c r="B37" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Réquisitions de la fenêtre.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="0"/>
-    </row>
+          <t>10. REQUISITIONS</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Réquisitions de la fenêtre.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38"/>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONTRÔLE AVANT ENVOI</t>
-        </is>
-      </c>
-      <c r="B39" s="0"/>
+          <t>CONTRÔLE AVANT ENVOI</t>
+        </is>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" s="0"/>
-      <c r="B40" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Chaque compteur nb_lignes_* de METADATA doit égaler le nombre de lignes réel de l'onglet (hors en-tête, hors exemple). Tout écart entraîne le rejet du lot entier.</t>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>1. Chaque compteur nb_lignes_* de METADATA doit égaler le nombre de lignes réel de l'onglet (hors en-tête, hors exemple). Tout écart entraîne le rejet du lot entier.</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="0"/>
-      <c r="B41" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2. Supprimer les 10 lignes d'exemple.</t>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2. Supprimer les 10 lignes d'exemple.</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="0"/>
-      <c r="B42" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3. Vérifier que tout site_id / produit_id / programme_id / transaction_id cité existe dans l'onglet de référence.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="0"/>
-    </row>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>3. Vérifier que tout site_id / produit_id / programme_id / transaction_id cité existe dans l'onglet de référence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43"/>
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">FOURNI PAR LA MISSION DQA</t>
-        </is>
-      </c>
-      <c r="B44" s="0"/>
+          <t>FOURNI PAR LA MISSION DQA</t>
+        </is>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" s="0"/>
-      <c r="B45" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">La liste des 40 sites du périmètre (pour dans_perimetre_dqa) et la liste des produits traceurs (filtre des onglets 6, 7, 9) sont transmises séparément et tenues à jour par la mission.</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="0"/>
-    </row>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>La liste des 40 sites du périmètre (pour dans_perimetre_dqa) et la liste des produits traceurs (filtre des onglets 6, 7, 9) sont transmises séparément et tenues à jour par la mission.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46"/>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">POINTS À CONFIRMER PAR LA DAP</t>
-        </is>
-      </c>
-      <c r="B47" s="0"/>
+          <t>POINTS À CONFIRMER PAR LA DAP</t>
+        </is>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" s="0"/>
-      <c r="B48" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Existe-t-il un calendrier de périodes mSupply mensuelles (period / periodschedule) ?</t>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>1. Existe-t-il un calendrier de périodes mSupply mensuelles (period / periodschedule) ?</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="0"/>
-      <c r="B49" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2. « si » = facture fournisseur adressée au site, « rc » = réception enregistrée : confirmer.</t>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2. « si » = facture fournisseur adressée au site, « rc » = réception enregistrée : confirmer.</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="0"/>
-      <c r="B50" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3. Des pertes / casses / péremptions sont-elles parfois saisies hors ajustement d'inventaire ?</t>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>3. Des pertes / casses / péremptions sont-elles parfois saisies hors ajustement d'inventaire ?</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="0"/>
-      <c r="B51" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4. Les champs programid (transact, requisition, stock_take) sont-ils toujours renseignés ?</t>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>4. Les champs programid (transact, requisition, stock_take) sont-ils toujours renseignés ?</t>
         </is>
       </c>
     </row>
@@ -578,110 +893,113 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="19" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="24" customWidth="1"/>
-    <col min="5" max="5" width="22" customWidth="1"/>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">INVENTAIRE_LIGNES</t>
+          <t>INVENTAIRE_LIGNES</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">INVENTAIRE_LIGNES · une ligne (inventaire, produit, lot). TRACEURS UNIQUEMENT. Une seule ligne par clé, sans doublon.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="0"/>
-    </row>
+          <t>INVENTAIRE_LIGNES · une ligne (inventaire, produit, lot). TRACEURS UNIQUEMENT. Une seule ligne par clé, sans doublon.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4" ht="135" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Obligatoire. stock_take_lines.stock_take_id. Doit exister dans INVENTAIRES.</t>
+          <t>Obligatoire. stock_take_lines.stock_take_id. Doit exister dans INVENTAIRES.</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Obligatoire. stock_take_lines.item_id. Traceur uniquement.</t>
+          <t>Obligatoire. stock_take_lines.item_id. Traceur uniquement.</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Facultatif. stock_take_lines.batch.</t>
+          <t>Facultatif. stock_take_lines.batch.</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Obligatoire. stock_take_lines.snapshot_qty x snapshot_packsize.</t>
+          <t>Obligatoire. stock_take_lines.snapshot_qty x snapshot_packsize.</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Obligatoire. stock_take_lines.stock_take_qty.</t>
+          <t>Obligatoire. stock_take_lines.stock_take_qty.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">inventaire_id</t>
+          <t>inventaire_id</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">produit_id</t>
+          <t>produit_id</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">lot</t>
+          <t>lot</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">quantite_theorique</t>
+          <t>quantite_theorique</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">quantite_comptee</t>
+          <t>quantite_comptee</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">4591D2192431874B82A7AF28A4ABB691</t>
+          <t>00000000000000000000000000000008</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">01A354A2DA8CD0439B95A4F0D099BC40</t>
+          <t>00000000000000000000000000000007</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">5GK0829</t>
+          <t>5GK0829</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">180</t>
+          <t>180</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">175</t>
+          <t>175</t>
         </is>
       </c>
     </row>
@@ -692,222 +1010,225 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="24" customWidth="1"/>
-    <col min="6" max="6" width="22" customWidth="1"/>
-    <col min="7" max="7" width="21" customWidth="1"/>
-    <col min="8" max="8" width="25" customWidth="1"/>
-    <col min="9" max="9" width="20" customWidth="1"/>
-    <col min="10" max="10" width="16" customWidth="1"/>
-    <col min="11" max="11" width="25" customWidth="1"/>
-    <col min="12" max="12" width="22" customWidth="1"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="25" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="25" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">REQUISITIONS</t>
+          <t>REQUISITIONS</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">REQUISITIONS · une réquisition. Fenêtre = date_entered ou période couverte touchant la fenêtre.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="0"/>
-    </row>
+          <t>REQUISITIONS · une réquisition. Fenêtre = date_entered ou période couverte touchant la fenêtre.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4" ht="135" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Obligatoire. requisition.id.</t>
+          <t>Obligatoire. requisition.id.</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Obligatoire. requisition.store_id. Doit exister dans SITES.</t>
+          <t>Obligatoire. requisition.store_id. Doit exister dans SITES.</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Obligatoire si requisition.programid est renseigné.</t>
+          <t>Obligatoire si requisition.programid est renseigné.</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Facultatif. requisition.periodid.</t>
+          <t>Facultatif. requisition.periodid.</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Obligatoire. period.startdate de periodid ; à défaut, 1er jour du mois de date_stock_take.</t>
+          <t>Obligatoire. period.startdate de periodid ; à défaut, 1er jour du mois de date_stock_take.</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Obligatoire. period.enddate ; à défaut, dernier jour du même mois.</t>
+          <t>Obligatoire. period.enddate ; à défaut, dernier jour du même mois.</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Obligatoire. requisition.date_entered.</t>
+          <t>Obligatoire. requisition.date_entered.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Facultatif. requisition.date_stock_take.</t>
+          <t>Facultatif. requisition.date_stock_take.</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Obligatoire si la réquisition a été réceptionnée. requisition.date_order_received.</t>
+          <t>Obligatoire si la réquisition a été réceptionnée. requisition.date_order_received.</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Obligatoire. requisition.status.</t>
+          <t>Obligatoire. requisition.status.</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Facultatif. requisition.authorisationstatus.</t>
+          <t>Facultatif. requisition.authorisationstatus.</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Obligatoire. Urgente si requisition.is_emergency, sinon Ordinaire.</t>
+          <t>Obligatoire. Urgente si requisition.is_emergency, sinon Ordinaire.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">requisition_id</t>
+          <t>requisition_id</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">site_id</t>
+          <t>site_id</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">programme_id</t>
+          <t>programme_id</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">periode_id</t>
+          <t>periode_id</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">mois_couvert_debut</t>
+          <t>mois_couvert_debut</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">mois_couvert_fin</t>
+          <t>mois_couvert_fin</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">date_soumission</t>
+          <t>date_soumission</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">date_inventaire_ref</t>
+          <t>date_inventaire_ref</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">date_reception</t>
+          <t>date_reception</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">statut</t>
+          <t>statut</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">statut_autorisation</t>
+          <t>statut_autorisation</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">type_requisition</t>
+          <t>type_requisition</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">27CEECD5FFBBFE4F9727C18FA3872B3A</t>
+          <t>00000000000000000000000000000004</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2BDAD2F787F1C045A28E2A35277F5184</t>
+          <t>00000000000000000000000000000006</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">A1B2C3D4E5F6...</t>
+          <t>A1B2C3D4E5F6...</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">P-2026-07</t>
+          <t>P-2026-07</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-31</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-05</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-30</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-20</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">fn</t>
+          <t>fn</t>
         </is>
       </c>
       <c r="K6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">authorised</t>
+          <t>authorised</t>
         </is>
       </c>
       <c r="L6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ordinaire</t>
+          <t>Ordinaire</t>
         </is>
       </c>
     </row>
@@ -918,295 +1239,294 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="30" customWidth="1"/>
-    <col min="2" max="2" width="26" customWidth="1"/>
-    <col min="3" max="3" width="80" customWidth="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="80" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">METADATA</t>
-        </is>
-      </c>
-      <c r="B1" s="0"/>
-      <c r="C1" s="0"/>
+          <t>METADATA</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Informations sur l'extraction. Renseigner la colonne « Valeur » (fond jaune).</t>
-        </is>
-      </c>
-      <c r="B2" s="0"/>
-      <c r="C2" s="0"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="0"/>
-    </row>
+          <t>Informations sur l'extraction. Renseigner la colonne « Valeur » (fond jaune).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Champ</t>
+          <t>Champ</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valeur</t>
+          <t>Valeur</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Consigne</t>
+          <t>Consigne</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">date_extraction</t>
-        </is>
-      </c>
-      <c r="B5" s="7"/>
+          <t>date_extraction</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n"/>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Date d'exécution de l'extraction (AAAA-MM-JJ).</t>
+          <t>Date d'exécution de l'extraction (AAAA-MM-JJ).</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">cycle_paqd</t>
-        </is>
-      </c>
-      <c r="B6" s="7"/>
+          <t>cycle_paqd</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="n"/>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cycle PAQD couvert, format AAAA-CN (ex. 2026-C2).</t>
+          <t>Cycle PAQD couvert, format AAAA-CN (ex. 2026-C2).</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">mois_paqd</t>
-        </is>
-      </c>
-      <c r="B7" s="7"/>
+          <t>mois_paqd</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="n"/>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">M+1, M+2, M+3 ou M+4.</t>
+          <t>M+1, M+2, M+3 ou M+4.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">mois_debut</t>
-        </is>
-      </c>
-      <c r="B8" s="7"/>
+          <t>mois_debut</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="n"/>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Premier jour du mois PAQD (AAAA-MM-JJ).</t>
+          <t>Premier jour du mois PAQD (AAAA-MM-JJ).</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">mois_fin</t>
-        </is>
-      </c>
-      <c r="B9" s="7"/>
+          <t>mois_fin</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="n"/>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dernier jour du mois PAQD.</t>
+          <t>Dernier jour du mois PAQD.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">fenetre_debut</t>
-        </is>
-      </c>
-      <c r="B10" s="7"/>
+          <t>fenetre_debut</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="n"/>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Premier jour de la fenêtre d'extraction (45 jours).</t>
+          <t>Premier jour de la fenêtre d'extraction (45 jours).</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">fenetre_fin</t>
-        </is>
-      </c>
-      <c r="B11" s="7"/>
+          <t>fenetre_fin</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="n"/>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dernier jour de la fenêtre.</t>
+          <t>Dernier jour de la fenêtre.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">version_msupply</t>
-        </is>
-      </c>
-      <c r="B12" s="7"/>
+          <t>version_msupply</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="n"/>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Version du serveur mSupply source (ex. V09.01.03).</t>
+          <t>Version du serveur mSupply source (ex. V09.01.03).</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">realisee_par</t>
-        </is>
-      </c>
-      <c r="B13" s="7"/>
+          <t>realisee_par</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="n"/>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nom et service de la personne ayant produit l'extraction.</t>
+          <t>Nom et service de la personne ayant produit l'extraction.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">nb_lignes_SITES</t>
-        </is>
-      </c>
-      <c r="B14" s="7"/>
+          <t>nb_lignes_SITES</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="n"/>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nombre de lignes de l'onglet SITES (hors en-tête et exemple).</t>
+          <t>Nombre de lignes de l'onglet SITES (hors en-tête et exemple).</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">nb_lignes_SITE_PROGRAMME</t>
-        </is>
-      </c>
-      <c r="B15" s="7"/>
+          <t>nb_lignes_SITE_PROGRAMME</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="n"/>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nombre de lignes de l'onglet SITE_PROGRAMME.</t>
+          <t>Nombre de lignes de l'onglet SITE_PROGRAMME.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">nb_lignes_PRODUITS</t>
-        </is>
-      </c>
-      <c r="B16" s="7"/>
+          <t>nb_lignes_PRODUITS</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="n"/>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nombre de lignes de l'onglet PRODUITS.</t>
+          <t>Nombre de lignes de l'onglet PRODUITS.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">nb_lignes_TRANSACTIONS</t>
-        </is>
-      </c>
-      <c r="B17" s="7"/>
+          <t>nb_lignes_TRANSACTIONS</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="n"/>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nombre de lignes de l'onglet TRANSACTIONS.</t>
+          <t>Nombre de lignes de l'onglet TRANSACTIONS.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">nb_lignes_LIGNES_TRANSACTIONS</t>
-        </is>
-      </c>
-      <c r="B18" s="7"/>
+          <t>nb_lignes_LIGNES_TRANSACTIONS</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="n"/>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nombre de lignes de l'onglet LIGNES_TRANSACTIONS.</t>
+          <t>Nombre de lignes de l'onglet LIGNES_TRANSACTIONS.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">nb_lignes_STOCK_ACTUEL</t>
-        </is>
-      </c>
-      <c r="B19" s="7"/>
+          <t>nb_lignes_STOCK_ACTUEL</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="n"/>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nombre de lignes de l'onglet STOCK_ACTUEL.</t>
+          <t>Nombre de lignes de l'onglet STOCK_ACTUEL.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">nb_lignes_INVENTAIRES</t>
-        </is>
-      </c>
-      <c r="B20" s="7"/>
+          <t>nb_lignes_INVENTAIRES</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="n"/>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nombre de lignes de l'onglet INVENTAIRES.</t>
+          <t>Nombre de lignes de l'onglet INVENTAIRES.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">nb_lignes_INVENTAIRE_LIGNES</t>
-        </is>
-      </c>
-      <c r="B21" s="7"/>
+          <t>nb_lignes_INVENTAIRE_LIGNES</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="n"/>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nombre de lignes de l'onglet INVENTAIRE_LIGNES.</t>
+          <t>Nombre de lignes de l'onglet INVENTAIRE_LIGNES.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">nb_lignes_REQUISITIONS</t>
-        </is>
-      </c>
-      <c r="B22" s="7"/>
+          <t>nb_lignes_REQUISITIONS</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="n"/>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nombre de lignes de l'onglet REQUISITIONS.</t>
+          <t>Nombre de lignes de l'onglet REQUISITIONS.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">observations</t>
-        </is>
-      </c>
-      <c r="B23" s="7"/>
+          <t>observations</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="n"/>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Toute anomalie constatée pendant l'extraction (facultatif).</t>
+          <t>Toute anomalie constatée pendant l'extraction (facultatif).</t>
         </is>
       </c>
     </row>
@@ -1217,174 +1537,177 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="20" customWidth="1"/>
-    <col min="7" max="7" width="16" customWidth="1"/>
-    <col min="8" max="8" width="24" customWidth="1"/>
-    <col min="9" max="9" width="29" customWidth="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="29" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">SITES</t>
+          <t>SITES</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SITES · un site (magasin mSupply). Inclure tous les magasins actifs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="0"/>
-    </row>
+          <t>SITES · un site (magasin mSupply). Inclure tous les magasins actifs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4" ht="135" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Obligatoire. store.id (identifiant mSupply du magasin).</t>
+          <t>Obligatoire. store.id (identifiant mSupply du magasin).</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Obligatoire. store.code.</t>
+          <t>Obligatoire. store.code.</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Obligatoire. store.name.</t>
+          <t>Obligatoire. store.name.</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Obligatoire. name_category1.description (via store.name_id -&gt; name.category1_id).</t>
+          <t>Obligatoire. name_category1.description (via store.name_id -&gt; name.category1_id).</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Obligatoire. name_category1_level2.description (grand-parent de name_category1).</t>
+          <t>Obligatoire. name_category1_level2.description (grand-parent de name_category1).</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Obligatoire. name_category3.description. Libellé exact : CSU, CSR, ESPC, HG, CHR, CHU, District sanitaire.</t>
+          <t>Obligatoire. name_category3.description. Libellé exact : CSU, CSR, ESPC, HG, CHR, CHU, District sanitaire.</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Obligatoire. OUI si store.disabled = false.</t>
+          <t>Obligatoire. OUI si store.disabled = false.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Obligatoire. OUI/NON. Liste des 40 sites fournie par la mission DQA.</t>
+          <t>Obligatoire. OUI/NON. Liste des 40 sites fournie par la mission DQA.</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Obligatoire. 5 (CSU/CSR/ESPC), 7 (HG/CHR), 10 (CHU/District).</t>
+          <t>Obligatoire. 5 (CSU/CSR/ESPC), 7 (HG/CHR), 10 (CHU/District).</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">site_id</t>
+          <t>site_id</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">site_code</t>
+          <t>site_code</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">site_nom</t>
+          <t>site_nom</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">district</t>
+          <t>district</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">region</t>
+          <t>region</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">type_structure</t>
+          <t>type_structure</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">actif</t>
+          <t>actif</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">dans_perimetre_dqa</t>
+          <t>dans_perimetre_dqa</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">jour_limite_requisition</t>
+          <t>jour_limite_requisition</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2C9D4FBD2B33F848BC3BA96DC0F0D120</t>
+          <t>00000000000000000000000000000001</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">14048CSU0005</t>
+          <t>14048CSU0005</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">CSU LAOUDIBA</t>
+          <t>CSU LAOUDIBA</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">BONDOUKOU</t>
+          <t>BONDOUKOU</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">GONTOUGO</t>
+          <t>GONTOUGO</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ESPC</t>
+          <t>ESPC</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUI</t>
+          <t>OUI</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUI</t>
+          <t>OUI</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -1395,110 +1718,113 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="20" customWidth="1"/>
-    <col min="4" max="4" width="19" customWidth="1"/>
-    <col min="5" max="5" width="16" customWidth="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">SITE_PROGRAMME</t>
+          <t>SITE_PROGRAMME</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SITE_PROGRAMME · un couple (site, programme géré). Pilote le pilier P1.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="0"/>
-    </row>
+          <t>SITE_PROGRAMME · un couple (site, programme géré). Pilote le pilier P1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4" ht="135" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Obligatoire. Magasin (list_master_name_join.name_id -&gt; store). Doit exister dans SITES.</t>
+          <t>Obligatoire. Magasin (list_master_name_join.name_id -&gt; store). Doit exister dans SITES.</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Obligatoire. list_master.id où list_master.isprogram = true.</t>
+          <t>Obligatoire. list_master.id où list_master.isprogram = true.</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Obligatoire. list_master.code.</t>
+          <t>Obligatoire. list_master.code.</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Obligatoire. list_master.description.</t>
+          <t>Obligatoire. list_master.description.</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Obligatoire. OUI si rattachement actif et list_master.inactive = false.</t>
+          <t>Obligatoire. OUI si rattachement actif et list_master.inactive = false.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">site_id</t>
+          <t>site_id</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">programme_id</t>
+          <t>programme_id</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">programme_code</t>
+          <t>programme_code</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">programme_nom</t>
+          <t>programme_nom</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">actif</t>
+          <t>actif</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2C9D4FBD2B33F848BC3BA96DC0F0D120</t>
+          <t>00000000000000000000000000000001</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">A1B2C3D4E5F6...</t>
+          <t>A1B2C3D4E5F6...</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIH</t>
+          <t>VIH</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIH / Sida</t>
+          <t>VIH / Sida</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUI</t>
+          <t>OUI</t>
         </is>
       </c>
     </row>
@@ -1509,110 +1835,113 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="17" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="16" customWidth="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">PRODUITS</t>
+          <t>PRODUITS</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PRODUITS · un produit. Tous les produits (le marquage traceur est géré côté tableau de bord).</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="0"/>
-    </row>
+          <t>PRODUITS · un produit. Tous les produits (le marquage traceur est géré côté tableau de bord).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4" ht="135" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Obligatoire. item.id.</t>
+          <t>Obligatoire. item.id.</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Obligatoire. item.code.</t>
+          <t>Obligatoire. item.code.</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Obligatoire. item.item_name.</t>
+          <t>Obligatoire. item.item_name.</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Facultatif. Libellé de l'unité (item.unit_id).</t>
+          <t>Facultatif. Libellé de l'unité (item.unit_id).</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Facultatif. Codes des programmes contenant l'item (list_master_line), séparés par ;.</t>
+          <t>Facultatif. Codes des programmes contenant l'item (list_master_line), séparés par ;.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">produit_id</t>
+          <t>produit_id</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">produit_code</t>
+          <t>produit_code</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">produit_nom</t>
+          <t>produit_nom</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">unite</t>
+          <t>unite</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">programmes</t>
+          <t>programmes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">7A3592212253C14CA208DBD6815D3155</t>
+          <t>00000000000000000000000000000002</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">5060001-GTC</t>
+          <t>5060001-GTC</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">KIT ACCOUCHEMENT</t>
+          <t>KIT ACCOUCHEMENT</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">KIT</t>
+          <t>KIT</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">SR;GRATUITE</t>
+          <t>SR;GRATUITE</t>
         </is>
       </c>
     </row>
@@ -1623,250 +1952,253 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="22" customWidth="1"/>
-    <col min="6" max="6" width="16" customWidth="1"/>
-    <col min="7" max="7" width="16" customWidth="1"/>
-    <col min="8" max="8" width="16" customWidth="1"/>
-    <col min="9" max="9" width="17" customWidth="1"/>
-    <col min="10" max="10" width="23" customWidth="1"/>
-    <col min="11" max="11" width="20" customWidth="1"/>
-    <col min="12" max="12" width="20" customWidth="1"/>
-    <col min="13" max="13" width="23" customWidth="1"/>
-    <col min="14" max="14" width="17" customWidth="1"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="23" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="23" customWidth="1" min="13" max="13"/>
+    <col width="17" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">TRANSACTIONS</t>
+          <t>TRANSACTIONS</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">TRANSACTIONS · une transaction (en-tête). Fenêtre = confirm_date ou finalised_date dans la fenêtre.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="0"/>
-    </row>
+          <t>TRANSACTIONS · une transaction (en-tête). Fenêtre = confirm_date ou finalised_date dans la fenêtre.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4" ht="135" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Obligatoire. transact.id.</t>
+          <t>Obligatoire. transact.id.</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Obligatoire. transact.store_id. Doit exister dans SITES.</t>
+          <t>Obligatoire. transact.store_id. Doit exister dans SITES.</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Obligatoire. Valeur dérivée (voir §5.1 de la spécification). Valeurs : dispensation, distribution, facture_fournisseur, reception, ajustement_positif, ajustement_negatif, retour_fournisseur, retour_client, autre.</t>
+          <t>Obligatoire. Valeur dérivée (voir §5.1 de la spécification). Valeurs : dispensation, distribution, facture_fournisseur, reception, ajustement_positif, ajustement_negatif, retour_fournisseur, retour_client, autre.</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Obligatoire si transact.programid est renseigné dans mSupply.</t>
+          <t>Obligatoire si transact.programid est renseigné dans mSupply.</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Obligatoire. transact.type (ci, si, sc, cc, rc...).</t>
+          <t>Obligatoire. transact.type (ci, si, sc, cc, rc...).</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Obligatoire. transact.mode (store, dispensary...).</t>
+          <t>Obligatoire. transact.mode (store, dispensary...).</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Obligatoire. transact.status (fn = finalisée).</t>
+          <t>Obligatoire. transact.status (fn = finalisée).</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Obligatoire. OUI si transact.is_cancellation.</t>
+          <t>Obligatoire. OUI si transact.is_cancellation.</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Obligatoire. transact.entry_date.</t>
+          <t>Obligatoire. transact.entry_date.</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Facultatif. transact.confirm_date.</t>
+          <t>Facultatif. transact.confirm_date.</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Obligatoire si nature = reception. transact.ship_date.</t>
+          <t>Obligatoire si nature = reception. transact.ship_date.</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Facultatif. transact.requisition_id.</t>
+          <t>Facultatif. transact.requisition_id.</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Facultatif. transact.goods_received_id.</t>
+          <t>Facultatif. transact.goods_received_id.</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Obligatoire si nature = ajustement_positif ou ajustement_negatif. transact.comment.</t>
+          <t>Obligatoire si nature = ajustement_positif ou ajustement_negatif. transact.comment.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">transaction_id</t>
+          <t>transaction_id</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">site_id</t>
+          <t>site_id</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">nature</t>
+          <t>nature</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">programme_id</t>
+          <t>programme_id</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">type_transaction</t>
+          <t>type_transaction</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">mode</t>
+          <t>mode</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">statut</t>
+          <t>statut</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">annulation</t>
+          <t>annulation</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">date_saisie</t>
+          <t>date_saisie</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">date_confirmation</t>
+          <t>date_confirmation</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">date_livraison</t>
+          <t>date_livraison</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">requisition_id</t>
+          <t>requisition_id</t>
         </is>
       </c>
       <c r="M5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">goods_received_id</t>
+          <t>goods_received_id</t>
         </is>
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">commentaire</t>
+          <t>commentaire</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">458de7e0757411f1a120750a3f5057be</t>
+          <t>458de7e0757411f1a120750a3f5057be</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">930C2CE79051B44CA6293BC4D3C892A1</t>
+          <t>00000000000000000000000000000003</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">reception</t>
+          <t>reception</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">A1B2C3D4E5F6...</t>
+          <t>A1B2C3D4E5F6...</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">rc</t>
+          <t>rc</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">store</t>
+          <t>store</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">fn</t>
+          <t>fn</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">NON</t>
+          <t>NON</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-05</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-05</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="K6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-04</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="L6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">27CEECD5FFBBFE4F9727C18FA3872B3A</t>
-        </is>
-      </c>
-      <c r="M6" s="5"/>
+          <t>00000000000000000000000000000004</t>
+        </is>
+      </c>
+      <c r="M6" s="5" t="n"/>
       <c r="N6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reçu pour facture(s) 711</t>
+          <t>Reçu pour facture(s) 711</t>
         </is>
       </c>
     </row>
@@ -1877,190 +2209,193 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="20" customWidth="1"/>
-    <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="16" customWidth="1"/>
-    <col min="7" max="7" width="28" customWidth="1"/>
-    <col min="8" max="8" width="16" customWidth="1"/>
-    <col min="9" max="9" width="21" customWidth="1"/>
-    <col min="10" max="10" width="21" customWidth="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="21" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">LIGNES_TRANSACTIONS</t>
+          <t>LIGNES_TRANSACTIONS</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">LIGNES_TRANSACTIONS · une ligne (transaction, produit, lot). PRODUITS TRACEURS UNIQUEMENT.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="0"/>
-    </row>
+          <t>LIGNES_TRANSACTIONS · une ligne (transaction, produit, lot). PRODUITS TRACEURS UNIQUEMENT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4" ht="135" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Obligatoire. trans_line.id.</t>
+          <t>Obligatoire. trans_line.id.</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Obligatoire. trans_line.transaction_id. Doit exister dans TRANSACTIONS.</t>
+          <t>Obligatoire. trans_line.transaction_id. Doit exister dans TRANSACTIONS.</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Obligatoire. trans_line.item_id. Produit traceur uniquement.</t>
+          <t>Obligatoire. trans_line.item_id. Produit traceur uniquement.</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Facultatif. trans_line.program_id.</t>
+          <t>Facultatif. trans_line.program_id.</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Facultatif. trans_line.batch.</t>
+          <t>Facultatif. trans_line.batch.</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Obligatoire. trans_line.quantity (quantité réelle en conditionnement).</t>
+          <t>Obligatoire. trans_line.quantity (quantité réelle en conditionnement).</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Obligatoire. trans_line.pack_size (unités de dispensation par conditionnement).</t>
+          <t>Obligatoire. trans_line.pack_size (unités de dispensation par conditionnement).</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Obligatoire. trans_line.type (stock_in, stock_out, service...).</t>
+          <t>Obligatoire. trans_line.type (stock_in, stock_out, service...).</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Obligatoire. OUI si trans_line.is_from_inventory_adjustment.</t>
+          <t>Obligatoire. OUI si trans_line.is_from_inventory_adjustment.</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Facultatif. trans_line.expiry_date.</t>
+          <t>Facultatif. trans_line.expiry_date.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ligne_id</t>
+          <t>ligne_id</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">transaction_id</t>
+          <t>transaction_id</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">produit_id</t>
+          <t>produit_id</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">programme_id</t>
+          <t>programme_id</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">lot</t>
+          <t>lot</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">quantite</t>
+          <t>quantite</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">taille_conditionnement</t>
+          <t>taille_conditionnement</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">type_ligne</t>
+          <t>type_ligne</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">issu_ajustement</t>
+          <t>issu_ajustement</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">date_peremption</t>
+          <t>date_peremption</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">d77dfb90757411f1a120750a3f5057be</t>
+          <t>d77dfb90757411f1a120750a3f5057be</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">8b522a70757411f1a120750a3f5057be</t>
+          <t>8b522a70757411f1a120750a3f5057be</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">63F9223F15B06C4C854D2A96419C043C</t>
+          <t>00000000000000000000000000000005</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">A1B2C3D4E5F6...</t>
+          <t>A1B2C3D4E5F6...</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">MIW1024020</t>
+          <t>MIW1024020</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">30</t>
+          <t>30</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">stock_out</t>
+          <t>stock_out</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">NON</t>
+          <t>NON</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-31</t>
+          <t>2027-03-31</t>
         </is>
       </c>
     </row>
@@ -2071,126 +2406,129 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="25" customWidth="1"/>
-    <col min="5" max="5" width="21" customWidth="1"/>
-    <col min="6" max="6" width="16" customWidth="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">STOCK_ACTUEL</t>
+          <t>STOCK_ACTUEL</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">STOCK_ACTUEL · un lot en stock (site, produit, lot) à la date d'extraction. TRACEURS UNIQUEMENT.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="0"/>
-    </row>
+          <t>STOCK_ACTUEL · un lot en stock (site, produit, lot) à la date d'extraction. TRACEURS UNIQUEMENT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4" ht="135" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Obligatoire. item_line.store_id. Doit exister dans SITES.</t>
+          <t>Obligatoire. item_line.store_id. Doit exister dans SITES.</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Obligatoire. item_line.item_id. Traceur uniquement.</t>
+          <t>Obligatoire. item_line.item_id. Traceur uniquement.</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Facultatif. item_line.batch.</t>
+          <t>Facultatif. item_line.batch.</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Obligatoire. item_line.available.</t>
+          <t>Obligatoire. item_line.available.</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Facultatif. item_line.expiry_date.</t>
+          <t>Facultatif. item_line.expiry_date.</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Obligatoire. Date d'extraction (identique pour toutes les lignes).</t>
+          <t>Obligatoire. Date d'extraction (identique pour toutes les lignes).</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">site_id</t>
+          <t>site_id</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">produit_id</t>
+          <t>produit_id</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">lot</t>
+          <t>lot</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">quantite_disponible</t>
+          <t>quantite_disponible</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">date_peremption</t>
+          <t>date_peremption</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">date_photo</t>
+          <t>date_photo</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2BDAD2F787F1C045A28E2A35277F5184</t>
+          <t>00000000000000000000000000000006</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">01A354A2DA8CD0439B95A4F0D099BC40</t>
+          <t>00000000000000000000000000000007</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">5GK0829</t>
+          <t>5GK0829</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">18900</t>
+          <t>18900</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-09-30</t>
+          <t>2028-09-30</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-18</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
@@ -2201,138 +2539,173 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="19" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="21" customWidth="1"/>
-    <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="24" customWidth="1"/>
-    <col min="7" max="7" width="25" customWidth="1"/>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
+    <col width="25" customWidth="1" min="8" max="8"/>
+    <col width="25" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">INVENTAIRES</t>
+          <t>INVENTAIRES</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">INVENTAIRES · un inventaire (stock_take, en-tête). Fenêtre = stock_take_date dans la fenêtre.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="0"/>
-    </row>
+          <t>INVENTAIRES · un inventaire (stock_take, en-tête). Fenêtre = stock_take_date dans la fenêtre.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4" ht="135" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Obligatoire. stock_take.id.</t>
+          <t>Obligatoire. stock_take.id.</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Obligatoire. stock_take.store_id. Doit exister dans SITES.</t>
+          <t>Obligatoire. stock_take.store_id. Doit exister dans SITES.</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Obligatoire si stock_take.programid est renseigné.</t>
+          <t>Obligatoire si stock_take.programid est renseigné.</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Obligatoire. stock_take.stock_take_date.</t>
+          <t>Obligatoire. stock_take.stock_take_date.</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Obligatoire. stock_take.status (fn = finalisé).</t>
+          <t>Obligatoire. stock_take.status (fn = finalisé).</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Facultatif. stock_take.invad_additions_id (transaction d'ajustement positif liée).</t>
+          <t>Facultatif. stock_take.invad_additions_id (transaction d'ajustement positif liée).</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Facultatif. stock_take.invad_reductions_id (transaction d'ajustement négatif liée).</t>
+          <t>Facultatif. stock_take.invad_reductions_id (transaction d'ajustement négatif liée).</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Facultatif. stock_take.stock_take_time, format HH:MM:SS. Désigne l'inventaire finalisé en dernier quand un site en finalise plusieurs le même jour.</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>Facultatif. stock_take.serial_number (numéro attribué par mSupply à la création). Départage deux inventaires de même heure.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">inventaire_id</t>
+          <t>inventaire_id</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">site_id</t>
+          <t>site_id</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">programme_id</t>
+          <t>programme_id</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">date_inventaire</t>
+          <t>date_inventaire</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">statut</t>
+          <t>statut</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">invad_additions_id</t>
+          <t>invad_additions_id</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">invad_reductions_id</t>
+          <t>invad_reductions_id</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>heure_inventaire</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>numero_inventaire</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">4591D2192431874B82A7AF28A4ABB691</t>
+          <t>00000000000000000000000000000008</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">AB256D09C93B3E4F970CE4E309F2D476</t>
+          <t>00000000000000000000000000000009</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">A1B2C3D4E5F6...</t>
+          <t>A1B2C3D4E5F6...</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-29</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">fn</t>
-        </is>
-      </c>
-      <c r="F6" s="5"/>
+          <t>fn</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="n"/>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">9F3A11B2...</t>
+          <t>9F3A11B2...</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>10:42:00</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>1287</t>
         </is>
       </c>
     </row>

--- a/docs/Canevas_Extraction_mSupply_DQA_v2.xlsx
+++ b/docs/Canevas_Extraction_mSupply_DQA_v2.xlsx
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Nouvelle PSP-CI / DAP · Spécification v2.0 (2026-08-28)</t>
+          <t>Nouvelle PSP-CI / DAP · Spécification v2.4 (2026-10-19)</t>
         </is>
       </c>
     </row>
@@ -572,7 +572,7 @@
     <row r="13">
       <c r="B13" t="inlineStr">
         <is>
-          <t>Les 45 derniers jours à chaque extraction (et non « depuis le dernier envoi »). Ce recouvrement permet de rattraper une semaine oubliée.</t>
+          <t>Du 1er jour du 2e mois avant la date d'extraction jusqu'à la date d'extraction (extraction du 12 octobre : du 1er août au 12 octobre), à chaque extraction et non « depuis le dernier envoi ». Le mois M-2 est ainsi extrait en entier, et le recouvrement rattrape une semaine oubliée.</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Transactions de la fenêtre (en-têtes), qualifiées par « nature ».</t>
+          <t>Transactions de la fenêtre (en-têtes), qualifiées par « nature » ; toutes les factures fournisseur si.</t>
         </is>
       </c>
     </row>
@@ -802,7 +802,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Réquisitions de la fenêtre.</t>
+          <t>Réquisitions de la fenêtre, et celles citées par une facture fournisseur si.</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
     <row r="49">
       <c r="B49" t="inlineStr">
         <is>
-          <t>2. « si » = facture fournisseur adressée au site, « rc » = réception enregistrée : confirmer.</t>
+          <t>2. Résolu (2026-10-14) : « si » = facture fournisseur adressée au site (nw, cn, fn), « rc » = reçu de paiement, transmis en nature encaissement.</t>
         </is>
       </c>
     </row>
@@ -921,7 +921,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="135" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -1045,7 +1044,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="135" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -1265,7 +1263,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -1541,7 +1538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1553,6 +1550,7 @@
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
     <col width="29" customWidth="1" min="9" max="9"/>
+    <col width="29" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1598,7 +1596,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Obligatoire. name_category3.description. Libellé exact : CSU, CSR, ESPC, HG, CHR, CHU, District sanitaire.</t>
+          <t>Obligatoire. Libellé exact : ESPC, HG, CHR, CHU, District sanitaire. Le préfixe du nom du site (CSU, CSR..., CHR, HG, CHU, DISTRICT SANITAIRE) l'emporte sur name_category3.</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -1614,6 +1612,11 @@
       <c r="I4" s="3" t="inlineStr">
         <is>
           <t>Obligatoire. 5 (CSU/CSR/ESPC), 7 (HG/CHR), 10 (CHU/District).</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>Facultatif. Type déduit de la seule catégorie mSupply (name_category3). Vide si la catégorie ne désigne pas un type (NPSP). Différent de type_structure : catégorie à corriger dans mSupply.</t>
         </is>
       </c>
     </row>
@@ -1663,6 +1666,11 @@
           <t>jour_limite_requisition</t>
         </is>
       </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>type_structure_msupply</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -1710,7 +1718,13 @@
           <t>5</t>
         </is>
       </c>
-    </row>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>ESPC</t>
+        </is>
+      </c>
+    </row>
+    <row r="7"/>
   </sheetData>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1746,7 +1760,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="135" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -1863,7 +1876,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="135" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -1956,7 +1968,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:Q7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1973,6 +1985,9 @@
     <col width="20" customWidth="1" min="12" max="12"/>
     <col width="23" customWidth="1" min="13" max="13"/>
     <col width="17" customWidth="1" min="14" max="14"/>
+    <col width="17" customWidth="1" min="15" max="15"/>
+    <col width="17" customWidth="1" min="16" max="16"/>
+    <col width="17" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1985,7 +2000,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>TRANSACTIONS · une transaction (en-tête). Fenêtre = confirm_date ou finalised_date dans la fenêtre.</t>
+          <t>TRANSACTIONS : une transaction (en-tête). Fenêtre = confirm_date ou finalised_date dans la fenêtre ; factures fournisseur si : toutes (nw, cn, fn) dont entry_date est dans la fenêtre.</t>
         </is>
       </c>
     </row>
@@ -2003,7 +2018,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Obligatoire. Valeur dérivée (voir §5.1 de la spécification). Valeurs : dispensation, distribution, facture_fournisseur, reception, ajustement_positif, ajustement_negatif, retour_fournisseur, retour_client, autre.</t>
+          <t>Obligatoire. Valeur dérivée (voir §5.1 de la spécification). Valeurs : dispensation, distribution, facture_fournisseur, encaissement (rc, reçu de paiement), ajustement_positif, ajustement_negatif, retour_fournisseur, retour_client, autre.</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -2043,7 +2058,7 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>Obligatoire si nature = reception. transact.ship_date.</t>
+          <t>Facultatif. transact.ship_date.</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -2059,6 +2074,21 @@
       <c r="N4" s="3" t="inlineStr">
         <is>
           <t>Obligatoire si nature = ajustement_positif ou ajustement_negatif. transact.comment.</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>Obligatoire si statut = fn. transact.finalised_date (date de réception d'une facture si).</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>Facture si seulement : la livraison qui l'a produite (transact.linked_transaction_id, dans un sens ou dans l'autre). Vide si aucune (site livré par la NPSP).</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr">
+        <is>
+          <t>Facture si seulement : finalised_date de la livraison liée (mois où la facture doit être acceptée).</t>
         </is>
       </c>
     </row>
@@ -2133,6 +2163,21 @@
           <t>commentaire</t>
         </is>
       </c>
+      <c r="O5" s="4" t="inlineStr">
+        <is>
+          <t>date_finalisation</t>
+        </is>
+      </c>
+      <c r="P5" s="4" t="inlineStr">
+        <is>
+          <t>transaction_liee_id</t>
+        </is>
+      </c>
+      <c r="Q5" s="4" t="inlineStr">
+        <is>
+          <t>date_finalisation_liee</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -2147,7 +2192,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>reception</t>
+          <t>facture_fournisseur</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -2157,7 +2202,7 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>rc</t>
+          <t>si</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
@@ -2196,12 +2241,24 @@
         </is>
       </c>
       <c r="M6" s="5" t="n"/>
-      <c r="N6" s="5" t="inlineStr">
-        <is>
-          <t>Reçu pour facture(s) 711</t>
-        </is>
-      </c>
-    </row>
+      <c r="N6" s="5" t="n"/>
+      <c r="O6" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="P6" s="5" t="inlineStr">
+        <is>
+          <t>5b1e0c2a757411f1a120750a3f5057be</t>
+        </is>
+      </c>
+      <c r="Q6" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="7"/>
   </sheetData>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2242,7 +2299,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="135" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -2435,7 +2491,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="135" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -2571,7 +2626,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="135" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
